--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484795_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484795_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>L. VERDEGUER FERRER</t>
+          <t>M. RODILLA ALCAIDE</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.0092</v>
+        <v>4.5011</v>
       </c>
       <c r="E2" t="n">
-        <v>2.3689</v>
+        <v>2.2887</v>
       </c>
       <c r="F2" t="n">
-        <v>1.6403</v>
+        <v>2.2124</v>
       </c>
       <c r="G2" t="n">
-        <v>1.7288</v>
+        <v>0.168</v>
       </c>
       <c r="H2" t="n">
-        <v>2.4581</v>
+        <v>1.1551</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.7292999999999999</v>
+        <v>-0.9871</v>
       </c>
       <c r="J2" t="n">
-        <v>2.6064</v>
+        <v>0.5798</v>
       </c>
       <c r="K2" t="n">
-        <v>1.9072</v>
+        <v>0.5713</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6992</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.8774999999999999</v>
+        <v>-0.4118</v>
       </c>
       <c r="N2" t="n">
-        <v>0.551</v>
+        <v>0.5838</v>
       </c>
       <c r="O2" t="n">
-        <v>-1.4285</v>
+        <v>-0.9956</v>
       </c>
       <c r="P2" t="n">
-        <v>2.0757</v>
+        <v>2.2644</v>
       </c>
       <c r="Q2" t="n">
         <v>0</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0757</v>
+        <v>2.2644</v>
       </c>
       <c r="S2" t="n">
-        <v>1.8276</v>
+        <v>0.8236</v>
       </c>
       <c r="T2" t="n">
-        <v>1.3855</v>
+        <v>0.4638</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4421</v>
+        <v>0.3598</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.6229</v>
+        <v>1.2452</v>
       </c>
       <c r="W2" t="n">
-        <v>-1.6229</v>
+        <v>1.2452</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>M. RODILLA ALCAIDE</t>
+          <t>R. MALLIK BOUNAD</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.366</v>
+        <v>4.331</v>
       </c>
       <c r="E3" t="n">
-        <v>1.3917</v>
+        <v>5.4441</v>
       </c>
       <c r="F3" t="n">
-        <v>1.9743</v>
+        <v>-1.1131</v>
       </c>
       <c r="G3" t="n">
-        <v>0.168</v>
+        <v>3.3637</v>
       </c>
       <c r="H3" t="n">
-        <v>1.1551</v>
+        <v>4.9507</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.9871</v>
+        <v>-1.587</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5798</v>
+        <v>5.0908</v>
       </c>
       <c r="K3" t="n">
-        <v>0.5713</v>
+        <v>4.4482</v>
       </c>
       <c r="L3" t="n">
-        <v>0.008500000000000001</v>
+        <v>0.6425</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4118</v>
+        <v>-1.7271</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5838</v>
+        <v>0.5024</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9956</v>
+        <v>-2.2295</v>
       </c>
       <c r="P3" t="n">
-        <v>2.2644</v>
+        <v>1.5096</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2644</v>
+        <v>3.3966</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.3116</v>
+        <v>0.7029</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4333</v>
+        <v>0.3725</v>
       </c>
       <c r="U3" t="n">
-        <v>0.1217</v>
+        <v>0.3304</v>
       </c>
       <c r="V3" t="n">
-        <v>1.2452</v>
+        <v>-1.2452</v>
       </c>
       <c r="W3" t="n">
-        <v>1.2452</v>
+        <v>1.8678</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-3.113</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>R. MALLIK BOUNAD</t>
+          <t>L. VERDEGUER FERRER</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,67 +721,67 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0337</v>
+        <v>3.2164</v>
       </c>
       <c r="E4" t="n">
-        <v>4.332</v>
+        <v>1.9993</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.2983</v>
+        <v>1.217</v>
       </c>
       <c r="G4" t="n">
-        <v>3.3637</v>
+        <v>1.7288</v>
       </c>
       <c r="H4" t="n">
-        <v>4.9507</v>
+        <v>2.4581</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.587</v>
+        <v>-0.7292999999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>5.0908</v>
+        <v>2.6064</v>
       </c>
       <c r="K4" t="n">
-        <v>4.4482</v>
+        <v>1.9072</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6425</v>
+        <v>0.6992</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.7271</v>
+        <v>-0.8774999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5024</v>
+        <v>0.551</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.2295</v>
+        <v>-1.4285</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5096</v>
+        <v>2.0757</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.887</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>3.3966</v>
+        <v>2.0757</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5943000000000001</v>
+        <v>1.0348</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.7396</v>
+        <v>1.0159</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1452</v>
+        <v>0.0189</v>
       </c>
       <c r="V4" t="n">
-        <v>-1.2452</v>
+        <v>-1.6229</v>
       </c>
       <c r="W4" t="n">
-        <v>1.8678</v>
+        <v>-1.6229</v>
       </c>
       <c r="X4" t="n">
-        <v>-3.113</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.3019</v>
+        <v>1.8555</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4627</v>
+        <v>-0.0631</v>
       </c>
       <c r="F5" t="n">
-        <v>1.8392</v>
+        <v>1.9186</v>
       </c>
       <c r="G5" t="n">
         <v>0.3838</v>
@@ -844,13 +844,13 @@
         <v>1.5096</v>
       </c>
       <c r="S5" t="n">
-        <v>1.352</v>
+        <v>0.9056</v>
       </c>
       <c r="T5" t="n">
-        <v>1.2062</v>
+        <v>0.6804</v>
       </c>
       <c r="U5" t="n">
-        <v>0.1458</v>
+        <v>0.2252</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -865,7 +865,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ZURBRIGGEN</t>
+          <t>M. MARTINEZ HERNANDEZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6884</v>
+        <v>1.2636</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.5312</v>
+        <v>0.1789</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2196</v>
+        <v>1.0847</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1854</v>
+        <v>-0.5044</v>
       </c>
       <c r="H6" t="n">
-        <v>2.9973</v>
+        <v>2.3251</v>
       </c>
       <c r="I6" t="n">
-        <v>-4.1827</v>
+        <v>-2.8295</v>
       </c>
       <c r="J6" t="n">
-        <v>0.9373</v>
+        <v>0.9958</v>
       </c>
       <c r="K6" t="n">
-        <v>2.869</v>
+        <v>2.2453</v>
       </c>
       <c r="L6" t="n">
-        <v>-1.9316</v>
+        <v>-1.2495</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.1227</v>
+        <v>-1.5001</v>
       </c>
       <c r="N6" t="n">
-        <v>0.1284</v>
+        <v>0.0798</v>
       </c>
       <c r="O6" t="n">
-        <v>-2.2511</v>
+        <v>-1.58</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>-0.3774</v>
       </c>
       <c r="Q6" t="n">
         <v>-2.8305</v>
       </c>
       <c r="R6" t="n">
-        <v>2.8305</v>
+        <v>2.4531</v>
       </c>
       <c r="S6" t="n">
-        <v>0.9494</v>
+        <v>0.9001</v>
       </c>
       <c r="T6" t="n">
-        <v>0.1357</v>
+        <v>0.7684</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8137</v>
+        <v>0.1317</v>
       </c>
       <c r="V6" t="n">
-        <v>0.9244</v>
+        <v>1.2452</v>
       </c>
       <c r="W6" t="n">
-        <v>1.2262</v>
+        <v>1.2452</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>J. DALMAU ROIG</t>
+          <t>A. ZURBRIGGEN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.3707</v>
+        <v>1.0281</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.7422</v>
+        <v>0.1524</v>
       </c>
       <c r="F7" t="n">
-        <v>2.1129</v>
+        <v>0.8757</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.6628</v>
+        <v>-1.1854</v>
       </c>
       <c r="H7" t="n">
-        <v>1.2404</v>
+        <v>2.9973</v>
       </c>
       <c r="I7" t="n">
-        <v>-2.9032</v>
+        <v>-4.1827</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.2995</v>
+        <v>0.9373</v>
       </c>
       <c r="K7" t="n">
-        <v>0.6081</v>
+        <v>2.869</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.9076</v>
+        <v>-1.9316</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.3633</v>
+        <v>-2.1227</v>
       </c>
       <c r="N7" t="n">
-        <v>0.6324</v>
+        <v>0.1284</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.9956</v>
+        <v>-2.2511</v>
       </c>
       <c r="P7" t="n">
-        <v>0.3774</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.887</v>
+        <v>-2.8305</v>
       </c>
       <c r="R7" t="n">
-        <v>2.2644</v>
+        <v>2.8305</v>
       </c>
       <c r="S7" t="n">
-        <v>2.2597</v>
+        <v>1.2891</v>
       </c>
       <c r="T7" t="n">
-        <v>1.4443</v>
+        <v>0.8194</v>
       </c>
       <c r="U7" t="n">
-        <v>0.8154</v>
+        <v>0.4698</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.6036</v>
+        <v>0.9244</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2262</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.6036</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>M. MARTINEZ HERNANDEZ</t>
+          <t>P. HURYNOWICZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,64 +1033,64 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1289</v>
+        <v>0.1512</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.7971</v>
+        <v>0.2371</v>
       </c>
       <c r="F8" t="n">
-        <v>0.926</v>
+        <v>-0.0859</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5044</v>
+        <v>-0.0607</v>
       </c>
       <c r="H8" t="n">
-        <v>2.3251</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="I8" t="n">
-        <v>-2.8295</v>
+        <v>-0.1515</v>
       </c>
       <c r="J8" t="n">
-        <v>0.9958</v>
+        <v>0.0423</v>
       </c>
       <c r="K8" t="n">
-        <v>2.2453</v>
+        <v>0.0423</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.2495</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.5001</v>
+        <v>-0.103</v>
       </c>
       <c r="N8" t="n">
-        <v>0.0798</v>
+        <v>0.0485</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.58</v>
+        <v>-0.1515</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.3774</v>
+        <v>0.1887</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.8305</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>2.4531</v>
+        <v>0.1887</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.2346</v>
+        <v>0.0232</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.2076</v>
+        <v>0.1949</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.027</v>
+        <v>-0.1716</v>
       </c>
       <c r="V8" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>1.2452</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
         <v>0</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>P. HURYNOWICZ</t>
+          <t>J. DALMAU ROIG</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0965</v>
+        <v>-0.07240000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>0.0423</v>
+        <v>-2.053</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.1388</v>
+        <v>1.9806</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.0607</v>
+        <v>-1.6628</v>
       </c>
       <c r="H9" t="n">
-        <v>0.09080000000000001</v>
+        <v>1.2404</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.1515</v>
+        <v>-2.9032</v>
       </c>
       <c r="J9" t="n">
-        <v>0.0423</v>
+        <v>-1.2995</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0423</v>
+        <v>0.6081</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>-1.9076</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.103</v>
+        <v>-0.3633</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0485</v>
+        <v>0.6324</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1515</v>
+        <v>-0.9956</v>
       </c>
       <c r="P9" t="n">
-        <v>0.1887</v>
+        <v>0.3774</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.887</v>
       </c>
       <c r="R9" t="n">
-        <v>0.1887</v>
+        <v>2.2644</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2246</v>
+        <v>1.8166</v>
       </c>
       <c r="T9" t="n">
-        <v>0</v>
+        <v>1.1335</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2246</v>
+        <v>0.6831</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.6036</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.4578</v>
+        <v>-0.2647</v>
       </c>
       <c r="E10" t="n">
-        <v>0.7324000000000001</v>
+        <v>0.7139</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.1902</v>
+        <v>-0.9786</v>
       </c>
       <c r="G10" t="n">
         <v>0.8442</v>
@@ -1234,13 +1234,13 @@
         <v>2.8305</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.057</v>
+        <v>0.1361</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4173</v>
+        <v>0.3988</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4744</v>
+        <v>-0.2627</v>
       </c>
       <c r="V10" t="n">
         <v>-3.132</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.5369</v>
+        <v>-0.4517</v>
       </c>
       <c r="E11" t="n">
-        <v>0.9619</v>
+        <v>1.0207</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.4989</v>
+        <v>-1.4724</v>
       </c>
       <c r="G11" t="n">
         <v>0.8479</v>
@@ -1312,13 +1312,13 @@
         <v>0.7548</v>
       </c>
       <c r="S11" t="n">
-        <v>0.03</v>
+        <v>0.1152</v>
       </c>
       <c r="T11" t="n">
-        <v>0.238</v>
+        <v>0.2968</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.2081</v>
+        <v>-0.1816</v>
       </c>
       <c r="V11" t="n">
         <v>-2.1696</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-0.846</v>
+        <v>-1.833</v>
       </c>
       <c r="E12" t="n">
-        <v>-2.2707</v>
+        <v>-3.2047</v>
       </c>
       <c r="F12" t="n">
-        <v>1.4247</v>
+        <v>1.3718</v>
       </c>
       <c r="G12" t="n">
         <v>-3.199</v>
@@ -1390,13 +1390,13 @@
         <v>2.0757</v>
       </c>
       <c r="S12" t="n">
-        <v>2.5042</v>
+        <v>1.5172</v>
       </c>
       <c r="T12" t="n">
-        <v>1.9639</v>
+        <v>1.0299</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5403</v>
+        <v>0.4874</v>
       </c>
       <c r="V12" t="n">
         <v>0.6036</v>
@@ -1423,16 +1423,16 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>11.9616</v>
+        <v>13.7251</v>
       </c>
       <c r="E13" t="n">
-        <v>4.950699999999999</v>
+        <v>6.714299999999999</v>
       </c>
       <c r="F13" t="n">
         <v>7.0108</v>
       </c>
       <c r="G13" t="n">
-        <v>0.7240999999999991</v>
+        <v>0.7241000000000004</v>
       </c>
       <c r="H13" t="n">
         <v>19.017</v>
@@ -1453,7 +1453,7 @@
         <v>-9.045000000000002</v>
       </c>
       <c r="N13" t="n">
-        <v>3.0758</v>
+        <v>3.075799999999999</v>
       </c>
       <c r="O13" t="n">
         <v>-12.1207</v>
@@ -1468,13 +1468,13 @@
         <v>22.644</v>
       </c>
       <c r="S13" t="n">
-        <v>7.5008</v>
+        <v>9.2644</v>
       </c>
       <c r="T13" t="n">
-        <v>5.4104</v>
+        <v>7.174300000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>2.0901</v>
+        <v>2.0904</v>
       </c>
       <c r="V13" t="n">
         <v>-4.7549</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.969</v>
+        <v>4.7856</v>
       </c>
       <c r="E14" t="n">
-        <v>3.3651</v>
+        <v>3.6574</v>
       </c>
       <c r="F14" t="n">
-        <v>0.6038</v>
+        <v>1.1282</v>
       </c>
       <c r="G14" t="n">
         <v>5.2008</v>
@@ -1546,13 +1546,13 @@
         <v>1.6983</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.6054</v>
+        <v>-0.7887</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5879</v>
+        <v>-0.2956</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.0175</v>
+        <v>-0.4932</v>
       </c>
       <c r="V14" t="n">
         <v>0.5622</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.9966</v>
+        <v>1.023</v>
       </c>
       <c r="E15" t="n">
-        <v>2.4439</v>
+        <v>2.0542</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.4473</v>
+        <v>-1.0311</v>
       </c>
       <c r="G15" t="n">
         <v>3.0619</v>
@@ -1624,13 +1624,13 @@
         <v>2.0757</v>
       </c>
       <c r="S15" t="n">
-        <v>-1.0804</v>
+        <v>-1.054</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1234</v>
+        <v>-0.2664</v>
       </c>
       <c r="U15" t="n">
-        <v>-1.2038</v>
+        <v>-0.7876</v>
       </c>
       <c r="V15" t="n">
         <v>-0.0414</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.8332000000000001</v>
+        <v>0.3822</v>
       </c>
       <c r="E16" t="n">
-        <v>0.2725</v>
+        <v>-0.0198</v>
       </c>
       <c r="F16" t="n">
-        <v>0.5607</v>
+        <v>0.402</v>
       </c>
       <c r="G16" t="n">
         <v>-2.6191</v>
@@ -1702,13 +1702,13 @@
         <v>1.5096</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3768</v>
+        <v>-0.0742</v>
       </c>
       <c r="T16" t="n">
-        <v>0.2997</v>
+        <v>0.0074</v>
       </c>
       <c r="U16" t="n">
-        <v>0.0771</v>
+        <v>-0.08160000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>2.5094</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.4465</v>
+        <v>0.2235</v>
       </c>
       <c r="E17" t="n">
-        <v>1.3652</v>
+        <v>1.8523</v>
       </c>
       <c r="F17" t="n">
-        <v>-1.8117</v>
+        <v>-1.6289</v>
       </c>
       <c r="G17" t="n">
         <v>-0.3865</v>
@@ -1780,13 +1780,13 @@
         <v>1.5096</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6412</v>
+        <v>-0.9713000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.8818</v>
+        <v>-0.3946</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.7594</v>
+        <v>-0.5766</v>
       </c>
       <c r="V17" t="n">
         <v>1.2038</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. ORTOLA TOMAS</t>
+          <t>S. SIDDIQUE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6282</v>
+        <v>-1.0515</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.4255</v>
+        <v>-1.8265</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.2027</v>
+        <v>0.775</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.5295</v>
+        <v>-0.3161</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.8868</v>
+        <v>-1.8469</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3573</v>
+        <v>1.5309</v>
       </c>
       <c r="J18" t="n">
-        <v>0.1059</v>
+        <v>-1.0067</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.6018</v>
+        <v>-1.1301</v>
       </c>
       <c r="L18" t="n">
-        <v>0.7077</v>
+        <v>0.1234</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.6354</v>
+        <v>0.6906</v>
       </c>
       <c r="N18" t="n">
-        <v>-1.285</v>
+        <v>-0.7168</v>
       </c>
       <c r="O18" t="n">
-        <v>0.6496</v>
+        <v>1.4075</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.5661</v>
+        <v>-0.9435</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9435</v>
+        <v>-3.0192</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3774</v>
+        <v>2.0757</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.5326</v>
+        <v>-0.7354000000000001</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5879</v>
+        <v>-0.291</v>
       </c>
       <c r="U18" t="n">
-        <v>0.0553</v>
+        <v>-0.4443</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.9434</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>2.4904</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-1.547</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. SIDDIQUE</t>
+          <t>J. ORTOLA TOMAS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6794</v>
+        <v>-1.3972</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.8265</v>
+        <v>-1.0357</v>
       </c>
       <c r="F19" t="n">
-        <v>0.1472</v>
+        <v>-0.3615</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3161</v>
+        <v>-0.5295</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.8469</v>
+        <v>-1.8868</v>
       </c>
       <c r="I19" t="n">
-        <v>1.5309</v>
+        <v>1.3573</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.0067</v>
+        <v>0.1059</v>
       </c>
       <c r="K19" t="n">
-        <v>-1.1301</v>
+        <v>-0.6018</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1234</v>
+        <v>0.7077</v>
       </c>
       <c r="M19" t="n">
-        <v>0.6906</v>
+        <v>-0.6354</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.7168</v>
+        <v>-1.285</v>
       </c>
       <c r="O19" t="n">
-        <v>1.4075</v>
+        <v>0.6496</v>
       </c>
       <c r="P19" t="n">
+        <v>-0.5661</v>
+      </c>
+      <c r="Q19" t="n">
         <v>-0.9435</v>
       </c>
-      <c r="Q19" t="n">
-        <v>-3.0192</v>
-      </c>
       <c r="R19" t="n">
-        <v>2.0757</v>
+        <v>0.3774</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.3632</v>
+        <v>-0.3016</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.291</v>
+        <v>-0.1981</v>
       </c>
       <c r="U19" t="n">
-        <v>-1.0722</v>
+        <v>-0.1034</v>
       </c>
       <c r="V19" t="n">
-        <v>0.9434</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>2.4904</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.547</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.698</v>
+        <v>-2.2601</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.3151</v>
+        <v>-1.9254</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.383</v>
+        <v>-0.3348</v>
       </c>
       <c r="G20" t="n">
         <v>0.2607</v>
@@ -2014,13 +2014,13 @@
         <v>2.0757</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.3132</v>
+        <v>-0.8753</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.823</v>
+        <v>-0.4333</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.4902</v>
+        <v>-0.442</v>
       </c>
       <c r="V20" t="n">
         <v>0.2414</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.8517</v>
+        <v>-3.545</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.8412</v>
+        <v>-2.7437</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.0105</v>
+        <v>-0.8012</v>
       </c>
       <c r="G21" t="n">
         <v>-3.1055</v>
@@ -2092,13 +2092,13 @@
         <v>0.7548</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.8783</v>
+        <v>-0.5715</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.4086</v>
+        <v>-0.3112</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.4696</v>
+        <v>-0.2604</v>
       </c>
       <c r="V21" t="n">
         <v>0.3208</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-7.4565</v>
+        <v>-8.173400000000001</v>
       </c>
       <c r="E22" t="n">
-        <v>-6.0493</v>
+        <v>-7.0236</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.4072</v>
+        <v>-1.1497</v>
       </c>
       <c r="G22" t="n">
         <v>-2.2909</v>
@@ -2170,13 +2170,13 @@
         <v>2.0757</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5367</v>
+        <v>-0.1802</v>
       </c>
       <c r="T22" t="n">
-        <v>1.0669</v>
+        <v>0.0925</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.5302</v>
+        <v>-0.2727</v>
       </c>
       <c r="V22" t="n">
         <v>-0.9848</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-11.9615</v>
+        <v>-10.0129</v>
       </c>
       <c r="E23" t="n">
-        <v>-7.0109</v>
+        <v>-7.0108</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.950699999999999</v>
+        <v>-3.002</v>
       </c>
       <c r="G23" t="n">
         <v>-0.7241999999999993</v>
@@ -2248,13 +2248,13 @@
         <v>14.1525</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.5008</v>
+        <v>-5.5522</v>
       </c>
       <c r="T23" t="n">
-        <v>-2.0902</v>
+        <v>-2.0903</v>
       </c>
       <c r="U23" t="n">
-        <v>-5.4105</v>
+        <v>-3.4618</v>
       </c>
       <c r="V23" t="n">
         <v>4.7548</v>
